--- a/yolo11_pose_run-batch4_重新標註-2/訓練摘要.xlsx
+++ b/yolo11_pose_run-batch4_重新標註-2/訓練摘要.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\小專題\code\yolo11_pose_run-batch4_重新標註-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A34BE20-5D06-4330-BD81-18A9F4E57444}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D58940-1A44-4FFC-B4BC-2208E38EE33E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t>train張數</t>
   </si>
@@ -392,7 +392,15 @@
     <t>141_jpg.rf.048dbc595653920138dbb767e54ff545.jpg</t>
   </si>
   <si>
-    <t>總額：</t>
+    <t>train：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>valid：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>總：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -870,6 +878,12 @@
       <c r="D2">
         <v>0</v>
       </c>
+      <c r="G2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2">
+        <v>56</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -883,6 +897,13 @@
       </c>
       <c r="D3">
         <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3">
+        <f>SUM(H1:H2)</f>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
